--- a/add-info-dmp/ig/StructureDefinition-DocumentEntry.xlsx
+++ b/add-info-dmp/ig/StructureDefinition-DocumentEntry.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-19T16:11:49+00:00</t>
+    <t>2025-08-01T13:09:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -231,7 +231,7 @@
     <t>Constraint(s)</t>
   </si>
   <si>
-    <t>Mapping: null</t>
+    <t>Mapping: DocumentEntryCDA</t>
   </si>
   <si>
     <t/>
@@ -491,10 +491,10 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Cette métadonnée contient les codes, libellés et codes système représentant :  • un évènement documenté (acte, traitement, diagnostic, etc…), • une modalité d'acquisition (contexte imagerie), • une région anatomique (contexte imagerie). </t>
-  </si>
-  <si>
-    <t>Cette métadonnée contient les codes, libellés et codes système représentant :  • un évènement documenté (acte, traitement, diagnostic, etc…), • une modalité d'acquisition (contexte imagerie), • une région anatomique (contexte imagerie).</t>
+    <t xml:space="preserve">Cette métadonnée contient les codes, libellés et codes système représentant :  -un évènement documenté (acte, traitement, diagnostic, etc…), -une modalité d'acquisition (contexte imagerie), -une région anatomique (contexte imagerie). </t>
+  </si>
+  <si>
+    <t>Cette métadonnée contient les codes, libellés et codes système représentant :  -un évènement documenté (acte, traitement, diagnostic, etc…), -une modalité d'acquisition (contexte imagerie), -une région anatomique (contexte imagerie).</t>
   </si>
   <si>
     <t>DocumentEntry.format</t>

--- a/add-info-dmp/ig/StructureDefinition-DocumentEntry.xlsx
+++ b/add-info-dmp/ig/StructureDefinition-DocumentEntry.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-08-01T13:09:58+00:00</t>
+    <t>2025-08-04T10:11:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/add-info-dmp/ig/StructureDefinition-DocumentEntry.xlsx
+++ b/add-info-dmp/ig/StructureDefinition-DocumentEntry.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-08-04T10:11:31+00:00</t>
+    <t>2025-08-04T13:10:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/add-info-dmp/ig/StructureDefinition-DocumentEntry.xlsx
+++ b/add-info-dmp/ig/StructureDefinition-DocumentEntry.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-08-04T13:10:17+00:00</t>
+    <t>2026-06-10T15:39:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -108,7 +108,7 @@
     <t>Base Definition</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/StructureDefinition/Base</t>
+    <t>http://hl7.org/fhir/StructureDefinition/Base|4.0.1</t>
   </si>
   <si>
     <t>Abstract</t>
@@ -302,7 +302,7 @@
     <t>preferred</t>
   </si>
   <si>
-    <t>https://mos.esante.gouv.fr/NOS/JDV_J52-AvailabilityStatus-CISIS/FHIR/JDV-J52-AvailabilityStatus-CISIS</t>
+    <t>https://mos.esante.gouv.fr/NOS/JDV_J52-AvailabilityStatus-CISIS/FHIR/JDV-J52-AvailabilityStatus-CISIS|20200424120000</t>
   </si>
   <si>
     <t>Non applicable, cette métadonnée n'est pas soumise par le système initiateur. Le registre du système cible gère cette information et fournit sa valeur en réponse à une requête stockée.</t>
@@ -463,7 +463,7 @@
 - Source : En fonction de l’interface fournie (ex. paramétrage fixe ou choix dans un menu déroulant).</t>
   </si>
   <si>
-    <t>https://mos.esante.gouv.fr/NOS/JDV_J06-XdsClassCode-CISIS/FHIR/JDV-J06-XdsClassCode-CISIS</t>
+    <t>https://mos.esante.gouv.fr/NOS/JDV_J06-XdsClassCode-CISIS/FHIR/JDV-J06-XdsClassCode-CISIS|20230922120000</t>
   </si>
   <si>
     <t>code@code (classCode est déduit de typeCode selon la table de correspondance entre ces deux métadonnées référencée dans les Nomenclatures des Objets de Santé (NOS) : ASS_X04-CorrespondanceType-Classe)</t>
@@ -481,7 +481,7 @@
     <t>**Confidentiality Code**</t>
   </si>
   <si>
-    <t>https://mos.esante.gouv.fr/NOS/JDV_J58-ConfidentialityCode-DMP/FHIR/JDV-J58-ConfidentialityCode-DMP</t>
+    <t>https://mos.esante.gouv.fr/NOS/JDV_J58-ConfidentialityCode-DMP/FHIR/JDV-J58-ConfidentialityCode-DMP|20200424120000</t>
   </si>
   <si>
     <t>DocumentEntry.eventCodeList</t>
@@ -506,7 +506,7 @@
     <t>**Format Code**</t>
   </si>
   <si>
-    <t>https://mos.esante.gouv.fr/NOS/JDV_J10-XdsFormatCode-CISIS/FHIR/JDV-J10-XdsFormatCode-CISIS</t>
+    <t>https://mos.esante.gouv.fr/NOS/JDV_J10-XdsFormatCode-CISIS/FHIR/JDV-J10-XdsFormatCode-CISIS|20251029120000</t>
   </si>
   <si>
     <t>DocumentEntry.healthcareFacilityTypeCode</t>
@@ -518,7 +518,7 @@
     <t>Healthcare Facility Type Code**</t>
   </si>
   <si>
-    <t>https://mos.esante.gouv.fr/NOS/JDV_J02-XdsHealthcareFacilityTypeCode-CISIS/FHIR/JDV-J02-XdsHealthcareFacilityTypeCode-CISIS</t>
+    <t>https://mos.esante.gouv.fr/NOS/JDV_J02-XdsHealthcareFacilityTypeCode-CISIS/FHIR/JDV-J02-XdsHealthcareFacilityTypeCode-CISIS|20260223120000</t>
   </si>
   <si>
     <t>DocumentEntry.practiceSetting</t>
@@ -530,7 +530,7 @@
     <t>**Practice Setting**</t>
   </si>
   <si>
-    <t>https://mos.esante.gouv.fr/NOS/JDV_J04-XdsPracticeSettingCode-CISIS/FHIR/JDV-J04-XdsPracticeSettingCode-CISIS</t>
+    <t>https://mos.esante.gouv.fr/NOS/JDV_J04-XdsPracticeSettingCode-CISIS/FHIR/JDV-J04-XdsPracticeSettingCode-CISIS|20240927120000</t>
   </si>
   <si>
     <t>DocumentEntry.type</t>
@@ -542,7 +542,7 @@
     <t>**Type Code**</t>
   </si>
   <si>
-    <t>https://mos.esante.gouv.fr/NOS/JDV_J07-XdsTypeCode-CISIS/FHIR/JDV-J07-XdsTypeCode-CISIS</t>
+    <t>https://mos.esante.gouv.fr/NOS/JDV_J07-XdsTypeCode-CISIS/FHIR/JDV-J07-XdsTypeCode-CISIS|20260601120000</t>
   </si>
   <si>
     <t>DocumentEntry.documentAvailability</t>
@@ -576,7 +576,7 @@
     <t>DocumentEntry.referenceIdList.CX1</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {elementdefinition-identifier}
+    <t xml:space="preserve">Extension {elementdefinition-identifier|5.3.0}
 </t>
   </si>
   <si>
@@ -595,7 +595,7 @@
     <t>Type d’identifiant</t>
   </si>
   <si>
-    <t>https://mos.esante.gouv.fr/NOS/JDV_J197-XdsTypesIdentifiantsReferenceId-CISIS/FHIR/JDV-J197-XdsTypesIdentifiantsReferenceId-CISIS</t>
+    <t>https://mos.esante.gouv.fr/NOS/JDV_J197-XdsTypesIdentifiantsReferenceId-CISIS/FHIR/JDV-J197-XdsTypesIdentifiantsReferenceId-CISIS|20220624120000</t>
   </si>
   <si>
     <t>DocumentEntry.version</t>
@@ -931,7 +931,7 @@
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="18.49609375" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="106.83203125" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="121.359375" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="17.65625" customWidth="true" bestFit="true"/>

--- a/add-info-dmp/ig/StructureDefinition-DocumentEntry.xlsx
+++ b/add-info-dmp/ig/StructureDefinition-DocumentEntry.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-10T15:39:40+00:00</t>
+    <t>2026-06-10T15:45:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -75,7 +75,7 @@
     <t>Jurisdiction</t>
   </si>
   <si>
-    <t>FRANCE</t>
+    <t>France (la)</t>
   </si>
   <si>
     <t>Description</t>

--- a/add-info-dmp/ig/StructureDefinition-DocumentEntry.xlsx
+++ b/add-info-dmp/ig/StructureDefinition-DocumentEntry.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-10T15:45:32+00:00</t>
+    <t>2026-06-10T15:59:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/add-info-dmp/ig/StructureDefinition-DocumentEntry.xlsx
+++ b/add-info-dmp/ig/StructureDefinition-DocumentEntry.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-10T15:59:45+00:00</t>
+    <t>2026-06-10T16:12:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/add-info-dmp/ig/StructureDefinition-DocumentEntry.xlsx
+++ b/add-info-dmp/ig/StructureDefinition-DocumentEntry.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-10T16:12:06+00:00</t>
+    <t>2026-06-10T16:18:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/add-info-dmp/ig/StructureDefinition-DocumentEntry.xlsx
+++ b/add-info-dmp/ig/StructureDefinition-DocumentEntry.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-10T16:18:52+00:00</t>
+    <t>2026-06-11T15:47:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/add-info-dmp/ig/StructureDefinition-DocumentEntry.xlsx
+++ b/add-info-dmp/ig/StructureDefinition-DocumentEntry.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-11T15:47:13+00:00</t>
+    <t>2026-06-11T15:59:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/add-info-dmp/ig/StructureDefinition-DocumentEntry.xlsx
+++ b/add-info-dmp/ig/StructureDefinition-DocumentEntry.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-11T15:59:09+00:00</t>
+    <t>2026-06-11T16:49:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/add-info-dmp/ig/StructureDefinition-DocumentEntry.xlsx
+++ b/add-info-dmp/ig/StructureDefinition-DocumentEntry.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-11T16:49:00+00:00</t>
+    <t>2026-06-12T14:52:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/add-info-dmp/ig/StructureDefinition-DocumentEntry.xlsx
+++ b/add-info-dmp/ig/StructureDefinition-DocumentEntry.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-12T14:52:39+00:00</t>
+    <t>2026-06-12T14:55:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/add-info-dmp/ig/StructureDefinition-DocumentEntry.xlsx
+++ b/add-info-dmp/ig/StructureDefinition-DocumentEntry.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-12T14:55:33+00:00</t>
+    <t>2026-06-12T14:56:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/add-info-dmp/ig/StructureDefinition-DocumentEntry.xlsx
+++ b/add-info-dmp/ig/StructureDefinition-DocumentEntry.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-12T14:56:09+00:00</t>
+    <t>2026-06-12T14:58:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/add-info-dmp/ig/StructureDefinition-DocumentEntry.xlsx
+++ b/add-info-dmp/ig/StructureDefinition-DocumentEntry.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-12T14:58:42+00:00</t>
+    <t>2026-06-12T15:04:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/add-info-dmp/ig/StructureDefinition-DocumentEntry.xlsx
+++ b/add-info-dmp/ig/StructureDefinition-DocumentEntry.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-12T15:04:49+00:00</t>
+    <t>2026-06-12T15:09:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/add-info-dmp/ig/StructureDefinition-DocumentEntry.xlsx
+++ b/add-info-dmp/ig/StructureDefinition-DocumentEntry.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-12T15:09:19+00:00</t>
+    <t>2026-06-12T15:31:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/add-info-dmp/ig/StructureDefinition-DocumentEntry.xlsx
+++ b/add-info-dmp/ig/StructureDefinition-DocumentEntry.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-12T15:31:20+00:00</t>
+    <t>2026-06-12T15:45:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/add-info-dmp/ig/StructureDefinition-DocumentEntry.xlsx
+++ b/add-info-dmp/ig/StructureDefinition-DocumentEntry.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-12T15:45:22+00:00</t>
+    <t>2026-06-12T16:24:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/add-info-dmp/ig/StructureDefinition-DocumentEntry.xlsx
+++ b/add-info-dmp/ig/StructureDefinition-DocumentEntry.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-12T16:24:39+00:00</t>
+    <t>2026-06-16T12:17:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/add-info-dmp/ig/StructureDefinition-DocumentEntry.xlsx
+++ b/add-info-dmp/ig/StructureDefinition-DocumentEntry.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-16T12:17:15+00:00</t>
+    <t>2026-06-16T12:25:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/add-info-dmp/ig/StructureDefinition-DocumentEntry.xlsx
+++ b/add-info-dmp/ig/StructureDefinition-DocumentEntry.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-16T12:25:33+00:00</t>
+    <t>2026-06-17T07:47:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/add-info-dmp/ig/StructureDefinition-DocumentEntry.xlsx
+++ b/add-info-dmp/ig/StructureDefinition-DocumentEntry.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-17T07:47:53+00:00</t>
+    <t>2026-06-17T07:58:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/add-info-dmp/ig/StructureDefinition-DocumentEntry.xlsx
+++ b/add-info-dmp/ig/StructureDefinition-DocumentEntry.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-17T07:58:49+00:00</t>
+    <t>2026-06-17T08:05:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/add-info-dmp/ig/StructureDefinition-DocumentEntry.xlsx
+++ b/add-info-dmp/ig/StructureDefinition-DocumentEntry.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-17T08:05:28+00:00</t>
+    <t>2026-06-17T08:38:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/add-info-dmp/ig/StructureDefinition-DocumentEntry.xlsx
+++ b/add-info-dmp/ig/StructureDefinition-DocumentEntry.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-17T08:38:09+00:00</t>
+    <t>2026-06-17T08:46:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/add-info-dmp/ig/StructureDefinition-DocumentEntry.xlsx
+++ b/add-info-dmp/ig/StructureDefinition-DocumentEntry.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-17T08:46:38+00:00</t>
+    <t>2026-06-17T08:50:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/add-info-dmp/ig/StructureDefinition-DocumentEntry.xlsx
+++ b/add-info-dmp/ig/StructureDefinition-DocumentEntry.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-17T08:50:19+00:00</t>
+    <t>2026-06-17T11:32:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/add-info-dmp/ig/StructureDefinition-DocumentEntry.xlsx
+++ b/add-info-dmp/ig/StructureDefinition-DocumentEntry.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-17T11:32:53+00:00</t>
+    <t>2026-06-17T11:35:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/add-info-dmp/ig/StructureDefinition-DocumentEntry.xlsx
+++ b/add-info-dmp/ig/StructureDefinition-DocumentEntry.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-17T11:35:28+00:00</t>
+    <t>2026-06-17T11:36:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/add-info-dmp/ig/StructureDefinition-DocumentEntry.xlsx
+++ b/add-info-dmp/ig/StructureDefinition-DocumentEntry.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-17T11:36:10+00:00</t>
+    <t>2026-06-17T12:12:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
